--- a/config/excel/CfgAssets.xlsx
+++ b/config/excel/CfgAssets.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgAssets" sheetId="1" r:id="R44fd00776ffa4336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgAssets" sheetId="1" r:id="Rde497512b3564c72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +49,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -90,6 +105,14 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -292,201 +315,181 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="11" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="11" t="str">
         <x:v>Address</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="12" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="12" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="14" t="str">
         <x:v># 固定表现资源角色</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>YooAsset逻辑地址</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="9" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="15" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="15" t="str">
         <x:v>SC_Expedition</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Room</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>RM_Prototype</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="9" t="str">
-        <x:v>Wall</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="str">
-        <x:v>PF_TestWall</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="9" t="str">
-        <x:v>Obstacle</x:v>
-      </x:c>
-      <x:c r="B7" s="9" t="str">
-        <x:v>PF_TestObstacle</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="9" t="str">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="15" t="str">
         <x:v>Player</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="str">
+      <x:c r="B5" s="15" t="str">
         <x:v>PF_TestPlayer</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="9" t="str">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="15" t="str">
         <x:v>Enemy</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>PF_TestEnemy</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="9" t="str">
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="15" t="str">
         <x:v>Boss</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="str">
+      <x:c r="B7" s="15" t="str">
         <x:v>PF_TestBoss</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="9" t="str">
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="15" t="str">
         <x:v>Npc</x:v>
       </x:c>
-      <x:c r="B11" s="9" t="str">
+      <x:c r="B8" s="15" t="str">
         <x:v>PF_TestNpc</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="9" t="str">
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="15" t="str">
         <x:v>Chest</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="str">
+      <x:c r="B9" s="15" t="str">
         <x:v>PF_TestChest</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="9" t="str">
-        <x:v>Exit</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="str">
-        <x:v>PF_TestExit</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="9" t="str">
-        <x:v>Extraction</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="str">
-        <x:v>PF_TestExtraction</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="9" t="str">
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="15" t="str">
         <x:v>Loot</x:v>
       </x:c>
-      <x:c r="B15" s="9" t="str">
+      <x:c r="B10" s="15" t="str">
         <x:v>PF_TestLoot</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="9" t="str">
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="15" t="str">
         <x:v>Projectile</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="str">
+      <x:c r="B11" s="15" t="str">
         <x:v>PF_TestProjectile</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="9" t="str">
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="15" t="str">
         <x:v>MeleeCue</x:v>
       </x:c>
-      <x:c r="B17" s="9" t="str">
+      <x:c r="B12" s="15" t="str">
         <x:v>PF_TestMeleeCue</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="9" t="str">
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="15" t="str">
         <x:v>HealthBar</x:v>
       </x:c>
-      <x:c r="B18" s="9" t="str">
+      <x:c r="B13" s="15" t="str">
         <x:v>PF_CombatHealthBar</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="48" customHeight="1">
-      <x:c r="A19" s="9" t="str">
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="15" t="str">
         <x:v>DamageText</x:v>
       </x:c>
-      <x:c r="B19" s="9" t="str">
+      <x:c r="B14" s="15" t="str">
         <x:v>PF_CombatDamageText</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="15" t="str">
+        <x:v>Hit</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="str">
+        <x:v>PF_CombatHit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>Telegraph</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>PF_CombatTelegraph</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>SwingSound</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="str">
+        <x:v>SFX_CombatSwing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="15" t="str">
+        <x:v>HitSound</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="str">
+        <x:v>SFX_CombatHit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="15" t="str">
+        <x:v>CriticalSound</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="str">
+        <x:v>SFX_CombatCritical</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" ht="48" customHeight="1">
-      <x:c r="A20" s="9" t="str">
-        <x:v>Hit</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="str">
-        <x:v>PF_CombatHit</x:v>
-      </x:c>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
-      <x:c r="A21" s="9" t="str">
-        <x:v>Telegraph</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="str">
-        <x:v>PF_CombatTelegraph</x:v>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
-      <x:c r="A22" s="9" t="str">
-        <x:v>SwingSound</x:v>
-      </x:c>
-      <x:c r="B22" s="9" t="str">
-        <x:v>SFX_CombatSwing</x:v>
-      </x:c>
+      <x:c r="A22"/>
+      <x:c r="B22"/>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
-      <x:c r="A23" s="9" t="str">
-        <x:v>HitSound</x:v>
-      </x:c>
-      <x:c r="B23" s="9" t="str">
-        <x:v>SFX_CombatHit</x:v>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
-      <x:c r="A24" s="9" t="str">
-        <x:v>CriticalSound</x:v>
-      </x:c>
-      <x:c r="B24" s="9" t="str">
-        <x:v>SFX_CombatCritical</x:v>
-      </x:c>
+      <x:c r="A24"/>
+      <x:c r="B24"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
